--- a/LISTA_USUARIOS.xlsx
+++ b/LISTA_USUARIOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franco\Desktop\sistema_solicitud\sistema_solicitud\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franco\Desktop\sistema_solicitud\New folder\sistema_solicitud\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35F3254-8FCC-4317-B3E2-729B053B3EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7006F4-8C49-4A01-AC49-5E65A9554BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="269">
   <si>
     <t>Nombres</t>
   </si>
@@ -824,6 +824,12 @@
   </si>
   <si>
     <t>Fisioterapeuta-Kinesiologa</t>
+  </si>
+  <si>
+    <t>Contabilidad - Caja Chica</t>
+  </si>
+  <si>
+    <t>Caja Chica</t>
   </si>
 </sst>
 </file>
@@ -929,6 +935,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -938,10 +948,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1287,19 +1293,19 @@
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="35.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
     <col min="6" max="6" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1314,7 +1320,7 @@
       <c r="D2" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>216</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -1334,7 +1340,7 @@
       <c r="D3" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1354,7 +1360,7 @@
       <c r="D4" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1374,7 +1380,7 @@
       <c r="D5" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1394,7 +1400,7 @@
       <c r="D6" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1414,7 +1420,7 @@
       <c r="D7" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1434,7 +1440,7 @@
       <c r="D8" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -1454,7 +1460,7 @@
       <c r="D9" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -1474,7 +1480,7 @@
       <c r="D10" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1494,7 +1500,7 @@
       <c r="D11" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1514,7 +1520,7 @@
       <c r="D12" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>217</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1534,7 +1540,7 @@
       <c r="D13" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1554,7 +1560,7 @@
       <c r="D14" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1574,7 +1580,7 @@
       <c r="D15" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -1594,8 +1600,8 @@
       <c r="D16" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>217</v>
+      <c r="E16" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>235</v>
@@ -1614,7 +1620,7 @@
       <c r="D17" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -1634,7 +1640,7 @@
       <c r="D18" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -1654,7 +1660,7 @@
       <c r="D19" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -1674,7 +1680,7 @@
       <c r="D20" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -1694,7 +1700,7 @@
       <c r="D21" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -1714,7 +1720,7 @@
       <c r="D22" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -1734,7 +1740,7 @@
       <c r="D23" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -1754,7 +1760,7 @@
       <c r="D24" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -1774,7 +1780,7 @@
       <c r="D25" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -1794,7 +1800,7 @@
       <c r="D26" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F26" s="2" t="s">
@@ -1814,7 +1820,7 @@
       <c r="D27" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -1834,7 +1840,7 @@
       <c r="D28" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F28" s="2" t="s">
@@ -1854,7 +1860,7 @@
       <c r="D29" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F29" s="2" t="s">
@@ -1874,7 +1880,7 @@
       <c r="D30" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F30" s="2" t="s">
@@ -1894,7 +1900,7 @@
       <c r="D31" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -1914,7 +1920,7 @@
       <c r="D32" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F32" s="2" t="s">
@@ -1934,7 +1940,7 @@
       <c r="D33" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="6" t="s">
         <v>217</v>
       </c>
       <c r="F33" s="2" t="s">
@@ -1954,7 +1960,7 @@
       <c r="D34" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F34" s="2" t="s">
@@ -1974,7 +1980,7 @@
       <c r="D35" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -1994,7 +2000,7 @@
       <c r="D36" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -2014,7 +2020,7 @@
       <c r="D37" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -2034,7 +2040,7 @@
       <c r="D38" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F38" s="2" t="s">
@@ -2054,7 +2060,7 @@
       <c r="D39" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F39" s="2" t="s">
@@ -2074,7 +2080,7 @@
       <c r="D40" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F40" s="2" t="s">
@@ -2094,7 +2100,7 @@
       <c r="D41" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -2114,7 +2120,7 @@
       <c r="D42" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F42" s="2" t="s">
@@ -2134,7 +2140,7 @@
       <c r="D43" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F43" s="2" t="s">
@@ -2154,7 +2160,7 @@
       <c r="D44" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F44" s="2" t="s">
@@ -2174,7 +2180,7 @@
       <c r="D45" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F45" s="2" t="s">
@@ -2194,7 +2200,7 @@
       <c r="D46" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F46" s="2" t="s">
@@ -2214,7 +2220,7 @@
       <c r="D47" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F47" s="2" t="s">
@@ -2232,9 +2238,9 @@
         <v>162</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E48" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>217</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -2254,7 +2260,7 @@
       <c r="D49" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F49" s="2" t="s">
@@ -2274,7 +2280,7 @@
       <c r="D50" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F50" s="2" t="s">
@@ -2282,14 +2288,14 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="7"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="9"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
@@ -2304,7 +2310,7 @@
       <c r="D52" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F52" s="2" t="s">
@@ -2324,7 +2330,7 @@
       <c r="D53" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F53" s="2" t="s">
@@ -2344,7 +2350,7 @@
       <c r="D54" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F54" s="2" t="s">
@@ -2362,10 +2368,10 @@
         <v>168</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>235</v>
@@ -2384,7 +2390,7 @@
       <c r="D56" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F56" s="2" t="s">
@@ -2404,7 +2410,7 @@
       <c r="D57" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F57" s="2" t="s">
@@ -2424,7 +2430,7 @@
       <c r="D58" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F58" s="2" t="s">
@@ -2444,7 +2450,7 @@
       <c r="D59" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F59" s="2" t="s">
@@ -2464,7 +2470,7 @@
       <c r="D60" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F60" s="2" t="s">
@@ -2484,7 +2490,7 @@
       <c r="D61" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F61" s="2" t="s">
@@ -2504,7 +2510,7 @@
       <c r="D62" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F62" s="2" t="s">
@@ -2524,7 +2530,7 @@
       <c r="D63" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="E63" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -2544,8 +2550,8 @@
       <c r="D64" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>217</v>
+      <c r="E64" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>257</v>
@@ -2564,7 +2570,7 @@
       <c r="D65" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F65" s="2" t="s">
@@ -2584,7 +2590,7 @@
       <c r="D66" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -2604,7 +2610,7 @@
       <c r="D67" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F67" s="2" t="s">
@@ -2624,7 +2630,7 @@
       <c r="D68" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E68" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F68" s="2" t="s">
@@ -2644,7 +2650,7 @@
       <c r="D69" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="E69" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F69" s="2" t="s">
@@ -2652,14 +2658,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="7"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
@@ -2674,7 +2680,7 @@
       <c r="D71" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="E71" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F71" s="2" t="s">
@@ -2694,7 +2700,7 @@
       <c r="D72" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E72" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F72" s="2" t="s">
@@ -2714,7 +2720,7 @@
       <c r="D73" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F73" s="2" t="s">
@@ -2734,7 +2740,7 @@
       <c r="D74" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F74" s="2" t="s">
@@ -2754,7 +2760,7 @@
       <c r="D75" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F75" s="2" t="s">
@@ -2774,7 +2780,7 @@
       <c r="D76" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E76" s="9" t="s">
+      <c r="E76" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F76" s="2" t="s">
@@ -2794,7 +2800,7 @@
       <c r="D77" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E77" s="9" t="s">
+      <c r="E77" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F77" s="2" t="s">
@@ -2814,7 +2820,7 @@
       <c r="D78" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="E78" s="6" t="s">
         <v>217</v>
       </c>
       <c r="F78" s="2" t="s">
@@ -2834,7 +2840,7 @@
       <c r="D79" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F79" s="2" t="s">
@@ -2854,7 +2860,7 @@
       <c r="D80" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E80" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F80" s="2" t="s">
@@ -2874,7 +2880,7 @@
       <c r="D81" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="E81" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F81" s="2" t="s">
@@ -2894,7 +2900,7 @@
       <c r="D82" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="E82" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F82" s="2" t="s">
@@ -2914,7 +2920,7 @@
       <c r="D83" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="E83" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F83" s="2" t="s">
@@ -2934,7 +2940,7 @@
       <c r="D84" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="E84" s="6" t="s">
         <v>219</v>
       </c>
       <c r="F84" s="2" t="s">
@@ -2954,7 +2960,7 @@
       <c r="D85" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F85" s="2" t="s">
@@ -2974,7 +2980,7 @@
       <c r="D86" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E86" s="9" t="s">
+      <c r="E86" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F86" s="2" t="s">
@@ -2994,7 +3000,7 @@
       <c r="D87" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F87" s="2" t="s">
@@ -3014,7 +3020,7 @@
       <c r="D88" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F88" s="2" t="s">
@@ -3034,7 +3040,7 @@
       <c r="D89" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F89" s="2" t="s">
@@ -3054,8 +3060,8 @@
       <c r="D90" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E90" s="9" t="s">
-        <v>218</v>
+      <c r="E90" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>232</v>
@@ -3074,7 +3080,7 @@
       <c r="D91" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E91" s="9" t="s">
+      <c r="E91" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F91" s="2" t="s">
@@ -3094,7 +3100,7 @@
       <c r="D92" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E92" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F92" s="2" t="s">
@@ -3114,7 +3120,7 @@
       <c r="D93" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="E93" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F93" s="2" t="s">
@@ -3134,7 +3140,7 @@
       <c r="D94" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="E94" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F94" s="2" t="s">
@@ -3154,7 +3160,7 @@
       <c r="D95" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="E95" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F95" s="2" t="s">
@@ -3174,7 +3180,7 @@
       <c r="D96" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E96" s="9" t="s">
+      <c r="E96" s="6" t="s">
         <v>218</v>
       </c>
       <c r="F96" s="2" t="s">

--- a/LISTA_USUARIOS.xlsx
+++ b/LISTA_USUARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franco\Desktop\sistema_solicitud\New folder\sistema_solicitud\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7006F4-8C49-4A01-AC49-5E65A9554BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5F563-6D30-44B5-B963-F692F7065D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9300" yWindow="1755" windowWidth="12915" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -836,7 +836,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,6 +848,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -922,10 +930,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -939,6 +948,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -949,7 +959,8 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1298,14 +1309,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1934,7 +1945,7 @@
       <c r="B33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -2241,7 +2252,7 @@
         <v>215</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>255</v>
@@ -2288,14 +2299,14 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="10"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
@@ -2364,7 +2375,7 @@
       <c r="B55" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D55" s="4" t="s">
@@ -2658,14 +2669,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="10"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
@@ -2814,14 +2825,14 @@
       <c r="B78" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="7" t="s">
         <v>190</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>215</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>261</v>
@@ -3054,7 +3065,7 @@
       <c r="B90" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D90" s="4" t="s">
@@ -3194,6 +3205,12 @@
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C33" r:id="rId1" xr:uid="{330E161C-A54C-4A83-9BC8-3B87D118ACB0}"/>
+    <hyperlink ref="C55" r:id="rId2" xr:uid="{E7298ADC-5B79-43C7-81DC-031BC7146A41}"/>
+    <hyperlink ref="C78" r:id="rId3" xr:uid="{FE2A8D02-FA74-4181-8372-15178926B95C}"/>
+    <hyperlink ref="C90" r:id="rId4" xr:uid="{D0538DA9-A632-47DA-9B71-3DDD76331E2B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>